--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mosart\Decimation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCFB3A06-6A04-43C5-A556-79A9CC0EDDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD77E837-5ACE-486A-81F9-F15CCB01554C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{EAC9642E-2780-4715-A237-6B734F742F4F}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>R1</t>
   </si>
@@ -100,16 +100,10 @@
     <t>9,9,9</t>
   </si>
   <si>
-    <t>max</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>Peak to peak</t>
-  </si>
-  <si>
     <t>19,17,15,13</t>
+  </si>
+  <si>
+    <t>17,15,13</t>
   </si>
 </sst>
 </file>
@@ -186,9 +180,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AADA55C8-D103-409C-96AB-A01B8178610C}" name="Table1" displayName="Table1" ref="A1:R1048576" totalsRowShown="0">
-  <autoFilter ref="A1:R1048576" xr:uid="{AADA55C8-D103-409C-96AB-A01B8178610C}"/>
-  <tableColumns count="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AADA55C8-D103-409C-96AB-A01B8178610C}" name="Table1" displayName="Table1" ref="A1:O1048576" totalsRowShown="0">
+  <autoFilter ref="A1:O1048576" xr:uid="{AADA55C8-D103-409C-96AB-A01B8178610C}"/>
+  <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{31F13482-C72E-40E7-8B70-3F9206D2090E}" name="Fs (Mhz)"/>
     <tableColumn id="2" xr3:uid="{8AB30B11-B2F0-49CD-A353-285996DAAB44}" name="F_signal (Khz)"/>
     <tableColumn id="3" xr3:uid="{41A95120-5268-48F4-A6D4-CFCEE0585DE7}" name="phase in (deg)"/>
@@ -204,9 +198,6 @@
     <tableColumn id="13" xr3:uid="{C0051476-536A-4277-BF1B-84C4FA290D94}" name="dc-component"/>
     <tableColumn id="14" xr3:uid="{2E9F2793-DAAB-4388-BA61-166118E00632}" name="P +ve"/>
     <tableColumn id="15" xr3:uid="{7426527E-FE61-4FD2-8671-FA8840BB0C15}" name="P -ve"/>
-    <tableColumn id="16" xr3:uid="{AC5E0175-BB8E-47A9-B2A1-967F88CDA155}" name="Peak to peak"/>
-    <tableColumn id="17" xr3:uid="{05EA2739-42B9-49A2-B3E5-4172D69679A8}" name="max"/>
-    <tableColumn id="18" xr3:uid="{F585CC4C-4242-400C-B725-EDF7E4F021C2}" name="min"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -509,13 +500,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D3580DB-E469-467F-8E83-9E3A210B0A07}">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="18" width="17.33203125" customWidth="1"/>
+    <col min="1" max="15" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -561,17 +552,8 @@
       <c r="O1" t="s">
         <v>16</v>
       </c>
-      <c r="P1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>12.8</v>
       </c>
@@ -618,7 +600,7 @@
         <v>499.03500000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>12.8</v>
       </c>
@@ -665,7 +647,7 @@
         <v>498.99599999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>12.8</v>
       </c>
@@ -712,7 +694,7 @@
         <v>499.02199999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>12.8</v>
       </c>
@@ -759,7 +741,7 @@
         <v>498.99799999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>12.8</v>
       </c>
@@ -806,7 +788,7 @@
         <v>498.99700000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>12.8</v>
       </c>
@@ -853,7 +835,7 @@
         <v>498.97399999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>12.8</v>
       </c>
@@ -900,7 +882,7 @@
         <v>499.02100000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>12.8</v>
       </c>
@@ -947,7 +929,7 @@
         <v>498.99599999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>12.8</v>
       </c>
@@ -993,17 +975,8 @@
       <c r="O10">
         <v>499.54500000000002</v>
       </c>
-      <c r="P10">
-        <v>1.986</v>
-      </c>
-      <c r="Q10">
-        <v>500.99299999999999</v>
-      </c>
-      <c r="R10">
-        <v>499.00700000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>12.8</v>
       </c>
@@ -1050,7 +1023,7 @@
         <v>499.02199999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>12.8</v>
       </c>
@@ -1073,7 +1046,7 @@
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I12">
         <v>9</v>
@@ -1097,7 +1070,7 @@
         <v>499.05900000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12.8</v>
       </c>
@@ -1120,7 +1093,7 @@
         <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I13">
         <v>9</v>
@@ -1142,6 +1115,53 @@
       </c>
       <c r="O13">
         <v>498.99700000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>12.8</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>32</v>
+      </c>
+      <c r="E14">
+        <v>8</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14">
+        <v>11</v>
+      </c>
+      <c r="J14">
+        <v>-3.3599999999999998E-2</v>
+      </c>
+      <c r="K14">
+        <v>-432.15300000000002</v>
+      </c>
+      <c r="L14">
+        <v>1.897</v>
+      </c>
+      <c r="M14">
+        <v>500</v>
+      </c>
+      <c r="N14">
+        <v>500.94900000000001</v>
+      </c>
+      <c r="O14">
+        <v>499.05099999999999</v>
       </c>
     </row>
   </sheetData>
